--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260911.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260911.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>6,279,000</t>
+          <t>6,323,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
@@ -633,210 +633,210 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>10,621,000</t>
+          <t>10,700,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>22,163,000</t>
+          <t>5,160,105,862</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>202610WTX</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>115/10台股期貨</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>37,056,000</t>
+          <t>550</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.43%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>49,710,000</t>
+          <t>22,333,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>6,282,000</t>
+          <t>37,056,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>4,367,438,146</t>
+          <t>50,095,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>10,202,000</t>
+          <t>6,331,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>21,691,000</t>
+          <t>10,500,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>11,759,000</t>
+          <t>21,691,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>564,000</t>
+          <t>11,848,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -880,29 +880,29 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>202609WTX</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>115/09台股期貨</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>568,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>6,846,000</t>
+          <t>6,897,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -963,166 +963,166 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>4,004,000</t>
+          <t>4,032,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>42,300,500</t>
+          <t>9,839,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>9,766,000</t>
+          <t>23,080,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>23,080,000</t>
+          <t>42,300,500</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>4,364,000</t>
+          <t>9,594,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>9,594,000</t>
+          <t>4,364,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,939,000</t>
+          <t>2,270,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,270,000</t>
+          <t>2,939,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -1161,95 +1161,95 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>18,088,000</t>
+          <t>18,248,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>14,684,000</t>
+          <t>15,578,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,295,000</t>
+          <t>14,684,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,706,859,590</t>
+          <t>5,324,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,169,000</t>
+          <t>2,633,551,204</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,83 +1261,83 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>4,995,000</t>
+          <t>42,169,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,686,000</t>
+          <t>6,478,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>17,277,000</t>
+          <t>6,686,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>9,700,000</t>
+          <t>17,277,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,110 +1349,110 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>6,199,000</t>
+          <t>9,757,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>7,991,000</t>
+          <t>26,620,004</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>26,620,004</t>
+          <t>7,991,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>9,344,000</t>
+          <t>10,287,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>10,287,000</t>
+          <t>9,344,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -1496,24 +1496,24 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>15,340,000</t>
+          <t>23,694,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>23,694,000</t>
+          <t>15,340,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1606,95 +1606,95 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>202610WTX</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>115/10台股期貨</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>52,799,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>52,799,000</t>
+          <t>1,593,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,593,000</t>
+          <t>18,948,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,948,000</t>
+          <t>16,823,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1716,95 +1716,73 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>16,823,000</t>
+          <t>18,491,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>長華電材</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>18,491,000</t>
+          <t>18,224,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>PB_NTD</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>長華電材</t>
+          <t>PAYABLES</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>18,224,000</t>
+          <t>-165,448,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>PB_NTD</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>PAYABLES</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>-16,919,045</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
+          <t>-0.11%</t>
         </is>
       </c>
     </row>
